--- a/docs/base_restritos.xlsx
+++ b/docs/base_restritos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thiag\Desktop\Analise_restritos\Analise_restritos\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59F96E2F-8138-409E-81A0-7F335F93632B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD226E70-42C6-4DB5-82F9-3AF226638A45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="base_restritos" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1203" uniqueCount="966">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1883" uniqueCount="973">
   <si>
     <t>Razão Social</t>
   </si>
@@ -2923,6 +2923,27 @@
   </si>
   <si>
     <t>89.539.977/0001-95</t>
+  </si>
+  <si>
+    <t>RADIAL DISTRIBUICAO LTDA EM RECUPERACAO JUDICIAL</t>
+  </si>
+  <si>
+    <t>JOSE MARIA MAGALHAES DE AZEVEDO</t>
+  </si>
+  <si>
+    <t>TELMO TONOLLI</t>
+  </si>
+  <si>
+    <t>CESAR DE ARAUJO MATA PIRES</t>
+  </si>
+  <si>
+    <t>GERALDO CORREIA SANTOS</t>
+  </si>
+  <si>
+    <t>HENRIQUE MARTINEZ ANDION</t>
+  </si>
+  <si>
+    <t>ONIX PARTICIPACAO</t>
   </si>
 </sst>
 </file>
@@ -3267,7 +3288,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:B602"/>
+  <dimension ref="A1:B948"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="86" style="2" bestFit="1" customWidth="1"/>
@@ -8088,6 +8109,2738 @@
         <v>16</v>
       </c>
     </row>
+    <row r="603" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A603" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B603" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="604" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A604" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B604" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="605" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A605" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B605" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="606" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A606" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B606" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="607" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A607" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B607" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="608" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A608" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B608" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="609" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A609" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B609" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="610" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A610" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B610" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="611" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A611" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B611" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="612" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A612" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B612" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="613" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A613" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B613" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="614" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A614" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B614" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="615" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A615" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B615" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="616" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A616" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B616" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="617" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A617" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B617" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="618" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A618" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B618" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="619" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A619" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B619" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="620" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A620" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B620" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="621" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A621" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B621" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="622" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A622" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B622" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="623" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A623" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B623" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="624" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A624" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B624" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="625" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A625" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B625" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="626" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A626" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B626" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="627" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A627" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B627" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="628" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A628" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B628" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="629" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A629" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B629" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="630" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A630" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B630" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="631" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A631" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B631" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="632" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A632" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B632" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="633" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A633" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B633" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="634" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A634" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B634" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="635" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A635" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B635" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="636" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A636" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B636" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="637" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A637" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B637" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="638" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A638" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B638" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="639" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A639" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B639" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="640" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A640" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B640" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="641" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A641" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B641" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="642" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A642" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B642" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="643" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A643" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B643" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="644" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A644" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B644" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="645" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A645" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B645" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="646" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A646" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B646" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="647" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A647" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B647" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="648" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A648" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B648" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="649" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A649" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B649" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="650" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A650" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B650" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="651" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A651" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B651" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="652" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A652" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B652" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="653" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A653" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B653" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="654" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A654" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B654" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="655" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A655" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B655" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="656" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A656" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B656" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="657" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A657" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B657" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="658" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A658" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B658" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="659" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A659" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B659" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="660" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A660" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B660" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="661" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A661" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B661" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="662" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A662" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B662" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="663" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A663" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B663" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="664" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A664" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B664" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="665" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A665" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B665" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="666" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A666" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B666" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="667" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A667" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B667" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="668" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A668" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B668" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="669" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A669" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B669" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="670" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A670" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B670" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="671" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A671" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B671" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="672" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A672" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B672" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="673" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A673" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B673" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="674" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A674" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B674" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="675" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A675" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B675" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="676" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A676" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B676" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="677" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A677" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B677" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="678" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A678" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B678" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="679" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A679" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="680" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A680" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B680" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="681" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A681" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B681" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="682" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A682" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B682" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="683" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A683" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B683" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="684" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A684" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B684" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="685" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A685" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B685" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="686" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A686" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B686" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="687" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A687" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B687" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="688" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A688" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B688" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="689" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A689" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B689" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="690" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A690" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B690" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="691" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A691" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B691" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="692" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A692" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B692" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="693" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A693" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B693" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="694" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A694" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B694" s="2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="695" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A695" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B695" s="2" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="696" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A696" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B696" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="697" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A697" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B697" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="698" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A698" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B698" s="2" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="699" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A699" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B699" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="700" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A700" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B700" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="701" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A701" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B701" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="702" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A702" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B702" s="2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="703" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A703" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B703" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="704" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A704" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B704" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="705" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A705" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B705" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="706" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A706" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B706" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="707" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A707" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B707" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="708" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A708" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B708" s="2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="709" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A709" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B709" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="710" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A710" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B710" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="711" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A711" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B711" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="712" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A712" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B712" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="713" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A713" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B713" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="714" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A714" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B714" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="715" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A715" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="B715" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="716" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A716" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="B716" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="717" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A717" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B717" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="718" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A718" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B718" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="719" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A719" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B719" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="720" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A720" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B720" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="721" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A721" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B721" s="2" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="722" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A722" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="B722" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="723" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A723" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B723" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="724" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A724" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B724" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="725" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A725" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B725" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="726" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A726" s="2" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="727" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A727" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="B727" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="728" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A728" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="B728" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="729" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A729" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="B729" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="730" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A730" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="B730" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="731" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A731" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B731" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="732" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A732" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="B732" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="733" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A733" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B733" s="2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="734" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A734" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="B734" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="735" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A735" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="B735" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="736" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A736" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="B736" s="2" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="737" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A737" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="B737" s="2" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="738" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A738" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="B738" s="2" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="739" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A739" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="B739" s="2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="740" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A740" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="B740" s="2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="741" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A741" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="B741" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="742" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A742" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="B742" s="2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="743" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A743" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="B743" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="744" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A744" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="B744" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="745" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A745" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B745" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="746" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A746" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="B746" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="747" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A747" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="B747" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="748" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A748" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="B748" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="749" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A749" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="B749" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="750" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A750" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="B750" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="751" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A751" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="B751" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="752" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A752" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="B752" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="753" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A753" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="B753" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="754" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A754" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="B754" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="755" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A755" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B755" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="756" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A756" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="B756" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="757" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A757" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="B757" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="758" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A758" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="B758" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="759" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A759" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="B759" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="760" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A760" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="B760" s="2" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="761" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A761" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="B761" s="2" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="762" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A762" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="B762" s="2" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="763" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A763" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="B763" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="764" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A764" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="B764" s="2" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="765" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A765" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="B765" s="2" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="766" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A766" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="B766" s="2" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="767" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A767" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="B767" s="2" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="768" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A768" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="B768" s="2" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="769" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A769" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B769" s="2" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="770" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A770" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="B770" s="2" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="771" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A771" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="B771" s="2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="772" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A772" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="B772" s="2" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="773" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A773" s="2" t="s">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="774" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A774" s="2" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="775" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A775" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="B775" s="2" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="776" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A776" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="B776" s="2" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="777" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A777" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="B777" s="2" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="778" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A778" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="B778" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="779" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A779" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="B779" s="2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="780" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A780" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B780" s="2" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="781" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A781" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="B781" s="2" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="782" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A782" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="B782" s="2" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="783" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A783" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="B783" s="2" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="784" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A784" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="B784" s="2" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="785" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A785" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="B785" s="2" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="786" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A786" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="B786" s="2" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="787" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A787" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="B787" s="2" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="788" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A788" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="B788" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="789" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A789" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="B789" s="2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="790" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A790" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="B790" s="2" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="791" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A791" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="B791" s="2" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="792" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A792" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="B792" s="2" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="793" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A793" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="B793" s="2" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="794" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A794" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="B794" s="2" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="795" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A795" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="B795" s="2" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="796" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A796" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="B796" s="2" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="797" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A797" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="B797" s="2" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="798" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A798" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="B798" s="2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="799" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A799" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="B799" s="2" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="800" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A800" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="B800" s="2" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="801" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A801" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="B801" s="2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="802" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A802" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="B802" s="2" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="803" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A803" s="2" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="804" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A804" s="2" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="805" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A805" s="2" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="806" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A806" s="2" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="807" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A807" s="2" t="s">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="808" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A808" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="B808" s="2" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="809" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A809" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="810" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A810" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="B810" s="2" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="811" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A811" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="B811" s="2" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="812" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A812" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="B812" s="2" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="813" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A813" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="B813" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="814" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A814" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="B814" s="2" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="815" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A815" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="B815" s="2" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="816" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A816" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="B816" s="2" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="817" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A817" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="B817" s="2" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="818" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A818" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="B818" s="2" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="819" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A819" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="B819" s="2" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="820" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A820" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="B820" s="2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="821" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A821" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="B821" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="822" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A822" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="B822" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="823" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A823" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="B823" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="824" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A824" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="B824" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="825" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A825" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="B825" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="826" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A826" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="B826" s="2" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="827" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A827" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="B827" s="2" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="828" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A828" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="B828" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="829" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A829" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B829" s="2" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="830" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A830" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="B830" s="2" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="831" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A831" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="B831" s="2" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="832" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A832" s="2" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="833" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A833" s="2" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="834" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A834" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="B834" s="2" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="835" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A835" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="B835" s="2" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="836" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A836" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="B836" s="2" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="837" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A837" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="B837" s="2" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="838" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A838" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="B838" s="2" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="839" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A839" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="B839" s="2" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="840" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A840" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="B840" s="2" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="841" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A841" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="B841" s="2" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="842" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A842" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="B842" s="2" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="843" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A843" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="B843" s="2" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="844" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A844" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="B844" s="2" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="845" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A845" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="B845" s="2" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="846" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A846" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="B846" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="847" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A847" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="B847" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="848" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A848" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="B848" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="849" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A849" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="B849" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="850" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A850" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="B850" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="851" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A851" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="B851" s="2" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="852" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A852" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="B852" s="2" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="853" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A853" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="B853" s="2" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="854" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A854" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="B854" s="2" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="855" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A855" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="B855" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="856" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A856" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="B856" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="857" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A857" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="B857" s="2" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="858" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A858" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="B858" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="859" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A859" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="B859" s="2" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="860" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A860" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="B860" s="2" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="861" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A861" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="B861" s="2" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="862" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A862" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="B862" s="2" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="863" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A863" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="B863" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="864" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A864" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="B864" s="2" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="865" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A865" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="B865" s="2" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="866" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A866" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="B866" s="2" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="867" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A867" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="B867" s="2" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="868" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A868" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="B868" s="2" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="869" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A869" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="B869" s="2" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="870" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A870" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="B870" s="2" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="871" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A871" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="B871" s="2" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="872" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A872" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="B872" s="2" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="873" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A873" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="B873" s="2" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="874" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A874" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="B874" s="2" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="875" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A875" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="B875" s="2" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="876" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A876" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="B876" s="2" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="877" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A877" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="B877" s="2" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="878" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A878" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="B878" s="2" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="879" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A879" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="B879" s="2" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="880" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A880" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="B880" s="2" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="881" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A881" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="B881" s="2" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="882" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A882" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="B882" s="2" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="883" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A883" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="B883" s="2" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="884" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A884" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="B884" s="2" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="885" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A885" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="B885" s="2" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="886" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A886" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="B886" s="2" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="887" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A887" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="B887" s="2" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="888" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A888" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="B888" s="2" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="889" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A889" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="B889" s="2" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="890" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A890" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="B890" s="2" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="891" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A891" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="B891" s="2" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="892" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A892" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="B892" s="2" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="893" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A893" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="B893" s="2" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="894" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A894" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="B894" s="2" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="895" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A895" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="B895" s="2" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="896" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A896" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="B896" s="2" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="897" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A897" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="B897" s="2" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="898" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A898" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="B898" s="2" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="899" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A899" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="B899" s="2" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="900" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A900" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="B900" s="2" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="901" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A901" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="B901" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="902" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A902" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="B902" s="2" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="903" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A903" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="B903" s="2" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="904" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A904" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="B904" s="2" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="905" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A905" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="B905" s="2" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="906" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A906" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="B906" s="2" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="907" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A907" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="B907" s="2" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="908" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A908" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="B908" s="2" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="909" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A909" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="B909" s="2" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="910" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A910" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="B910" s="2" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="911" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A911" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="B911" s="2" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="912" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A912" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="B912" s="2" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="913" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A913" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="B913" s="2" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="914" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A914" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="B914" s="2" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="915" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A915" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="B915" s="2" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="916" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A916" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="B916" s="2" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="917" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A917" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="B917" s="2" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="918" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A918" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="B918" s="2" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="919" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A919" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="B919" s="2" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="920" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A920" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="B920" s="2" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="921" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A921" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="B921" s="2" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="922" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A922" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="B922" s="2" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="923" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A923" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="B923" s="2" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="924" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A924" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="B924" s="2" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="925" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A925" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="B925" s="2" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="926" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A926" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="B926" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="927" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A927" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="B927" s="2" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="928" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A928" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="B928" s="2" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="929" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A929" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="B929" s="2" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="930" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A930" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="B930" s="2" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="931" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A931" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="B931" s="2" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="932" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A932" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="B932" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="933" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A933" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="B933" s="2" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="934" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A934" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="B934" s="2" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="935" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A935" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="B935" s="2" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="936" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A936" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="B936" s="2" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="937" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A937" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="B937" s="2" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="938" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A938" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="B938" s="2" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="939" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A939" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="B939" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="940" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A940" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="B940" s="2" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="941" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A941" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="B941" s="2" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="942" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A942" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="B942" s="2" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="943" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A943" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="B943" s="2" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="944" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A944" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="B944" s="2" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="945" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A945" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="B945" s="2" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="946" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A946" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="B946" s="2" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="947" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A947" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="B947" s="2" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="948" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A948" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="B948" s="2" t="s">
+        <v>579</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
